--- a/ROMI Pin Configuration Spreadsheet.xlsx
+++ b/ROMI Pin Configuration Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cpslo-my.sharepoint.com/personal/qpatters_calpoly_edu/Documents/405/405 Quinn and Jake/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="11_F25DC773A252ABDACC104886319969B05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D49DCA7D-9F9C-471E-BDCF-A778D80ADD44}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="11_F25DC773A252ABDACC104886319969B05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F62C995-1E42-4858-89A8-6ABE1D9071F6}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="89">
   <si>
     <t>Cable</t>
   </si>
@@ -147,18 +147,6 @@
     <t>Digital Output (PB5)</t>
   </si>
   <si>
-    <t>Timer 1 Ch 1 (PA9)</t>
-  </si>
-  <si>
-    <t>Timer 1 Ch 2 (PA8)</t>
-  </si>
-  <si>
-    <t>Timer 2 CH 1 (PA1)</t>
-  </si>
-  <si>
-    <t>Timer 2 Ch 2 (PA0)</t>
-  </si>
-  <si>
     <t>HC-05 Bluetooth Module</t>
   </si>
   <si>
@@ -280,13 +268,37 @@
   </si>
   <si>
     <t>GPIO (PA15)</t>
+  </si>
+  <si>
+    <t>BNO055 Datasheet</t>
+  </si>
+  <si>
+    <t>STM Datasheet</t>
+  </si>
+  <si>
+    <t>Nucleo Pinout Sheet</t>
+  </si>
+  <si>
+    <t>Useful Links</t>
+  </si>
+  <si>
+    <t>Timer 1 Ch 1 (PA8)</t>
+  </si>
+  <si>
+    <t>Timer 1 Ch 2 (PA9)</t>
+  </si>
+  <si>
+    <t>Timer 2 CH 1 (PA0)</t>
+  </si>
+  <si>
+    <t>Timer 2 Ch 2 (PA1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +314,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -683,7 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -709,7 +729,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -760,6 +779,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -828,7 +851,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>373376</xdr:colOff>
+      <xdr:colOff>251261</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>172363</xdr:rowOff>
     </xdr:to>
@@ -881,10 +904,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1157,7 +1176,7 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="22.796875" customWidth="1"/>
     <col min="7" max="7" width="12.06640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="9" max="9" width="17.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
@@ -1182,27 +1201,27 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B4" s="38"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
@@ -1213,14 +1232,14 @@
         <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="38"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="7">
         <v>1</v>
       </c>
@@ -1231,52 +1250,52 @@
         <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="39"/>
-      <c r="C6" s="20">
+      <c r="B6" s="42"/>
+      <c r="C6" s="19">
         <v>2</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="F6" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>1</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B8" s="41"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="5">
         <v>2</v>
       </c>
@@ -1289,12 +1308,12 @@
       <c r="F8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B9" s="41"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="5">
         <v>3</v>
       </c>
@@ -1305,14 +1324,14 @@
         <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B10" s="41"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="5">
         <v>1</v>
       </c>
@@ -1325,12 +1344,12 @@
       <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B11" s="41"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="5">
         <v>2</v>
       </c>
@@ -1343,88 +1362,88 @@
       <c r="F11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="42"/>
-      <c r="C12" s="16">
+      <c r="B12" s="45"/>
+      <c r="C12" s="15">
         <v>3</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>1</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="39"/>
-      <c r="C14" s="16">
+      <c r="B14" s="42"/>
+      <c r="C14" s="15">
         <v>2</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="12">
+      <c r="B15" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="11">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>45</v>
+      <c r="G15" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B16" s="44"/>
+      <c r="B16" s="47"/>
       <c r="C16" s="5">
         <v>2</v>
       </c>
@@ -1435,325 +1454,337 @@
         <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B17" s="44"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="5">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B18" s="47"/>
+      <c r="C18" s="10">
+        <v>4</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="44"/>
-      <c r="C18" s="11">
-        <v>4</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>1</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>45</v>
+      <c r="G19" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B20" s="44"/>
+      <c r="B20" s="47"/>
       <c r="C20" s="5">
         <v>2</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>45</v>
+      <c r="F20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B21" s="44"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="5">
         <v>3</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>45</v>
+      <c r="D21" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B22" s="44"/>
+      <c r="B22" s="47"/>
       <c r="C22" s="5">
         <v>4</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>45</v>
+      <c r="D22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B23" s="44"/>
+      <c r="B23" s="47"/>
       <c r="C23" s="5">
         <v>5</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B24" s="44"/>
+      <c r="D23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B24" s="47"/>
       <c r="C24" s="5">
         <v>6</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B25" s="44"/>
+      <c r="D24" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="47"/>
       <c r="C25" s="5">
         <v>7</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>45</v>
+      <c r="E25" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="44"/>
-      <c r="C26" s="25">
+      <c r="B26" s="47"/>
+      <c r="C26" s="24">
         <v>8</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>50</v>
+      <c r="D26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B27" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="12">
+      <c r="B27" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="11">
         <v>1</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="28" t="s">
-        <v>45</v>
+      <c r="G27" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B28" s="35"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="5">
         <v>2</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B29" s="35"/>
+      <c r="F28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B29" s="38"/>
       <c r="C29" s="5">
         <v>3</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>45</v>
+      <c r="E29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B30" s="35"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="5">
         <v>4</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="10" t="s">
+      <c r="E30" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="39"/>
+      <c r="C31" s="10">
+        <v>5</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B32" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="29">
+        <v>1</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="G30" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="36"/>
-      <c r="C31" s="11">
-        <v>5</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" s="26" t="s">
+      <c r="G32" s="27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="36"/>
+      <c r="C33" s="30">
+        <v>2</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="G31" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B32" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="30">
-        <v>1</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="33"/>
-      <c r="C33" s="31">
-        <v>2</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>45</v>
+      <c r="G33" s="28" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1768,8 +1799,12 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I26" r:id="rId1" xr:uid="{D1D17580-34B3-4C6C-9021-43ED92735AFE}"/>
+    <hyperlink ref="I27" r:id="rId2" xr:uid="{2DFA3FF4-38B6-4B53-8E03-E5504029D3D8}"/>
+    <hyperlink ref="I28" r:id="rId3" xr:uid="{BF653687-14B9-4F76-989A-0342E3981965}"/>
+    <hyperlink ref="I29" r:id="rId4" xr:uid="{D24C38C6-563F-4FAC-A43E-7B556D78903D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>